--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/88.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/88.xlsx
@@ -426,13 +426,13 @@
         <v>-12.77967567496229</v>
       </c>
       <c r="E2">
-        <v>-10.07740548188477</v>
+        <v>-8.750956574876023</v>
       </c>
       <c r="F2">
-        <v>3.840404639056686</v>
+        <v>4.035331914246719</v>
       </c>
       <c r="G2">
-        <v>-16.37710440616593</v>
+        <v>-16.95963793089271</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-12.20045664051357</v>
       </c>
       <c r="E3">
-        <v>-11.52411254464121</v>
+        <v>-7.884043624743641</v>
       </c>
       <c r="F3">
-        <v>3.761084728281901</v>
+        <v>3.326930756035162</v>
       </c>
       <c r="G3">
-        <v>-15.29348670861507</v>
+        <v>-15.35827739536415</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-11.52663908833438</v>
       </c>
       <c r="E4">
-        <v>-11.04882202669216</v>
+        <v>-9.274525154220846</v>
       </c>
       <c r="F4">
-        <v>3.808250657855518</v>
+        <v>4.060411481123618</v>
       </c>
       <c r="G4">
-        <v>-14.69443852746564</v>
+        <v>-14.53053672836186</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-10.84391970968579</v>
       </c>
       <c r="E5">
-        <v>-10.88144057042065</v>
+        <v>-9.799841724532632</v>
       </c>
       <c r="F5">
-        <v>3.755696960757576</v>
+        <v>4.44885811694486</v>
       </c>
       <c r="G5">
-        <v>-15.14519247645619</v>
+        <v>-15.14284364439607</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-10.14323702343321</v>
       </c>
       <c r="E6">
-        <v>-13.49397156713377</v>
+        <v>-12.23678567007234</v>
       </c>
       <c r="F6">
-        <v>4.091439447418908</v>
+        <v>4.103277649136817</v>
       </c>
       <c r="G6">
-        <v>-13.37803816504815</v>
+        <v>-13.26706867857178</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-9.44893447827277</v>
       </c>
       <c r="E7">
-        <v>-13.5024896267422</v>
+        <v>-10.11011917811618</v>
       </c>
       <c r="F7">
-        <v>4.744695965654864</v>
+        <v>4.527994317833453</v>
       </c>
       <c r="G7">
-        <v>-13.05719002301861</v>
+        <v>-14.42523158530319</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-8.751373658257876</v>
       </c>
       <c r="E8">
-        <v>-14.0631826360019</v>
+        <v>-12.666383885284</v>
       </c>
       <c r="F8">
-        <v>4.383484320461434</v>
+        <v>4.749302966162877</v>
       </c>
       <c r="G8">
-        <v>-11.49395704046583</v>
+        <v>-12.36942749778056</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-8.049682388252565</v>
       </c>
       <c r="E9">
-        <v>-14.78863964355669</v>
+        <v>-13.47571275993485</v>
       </c>
       <c r="F9">
-        <v>4.415334230126837</v>
+        <v>5.249872813385401</v>
       </c>
       <c r="G9">
-        <v>-11.09351676258113</v>
+        <v>-11.43095404830796</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-7.332050684919654</v>
       </c>
       <c r="E10">
-        <v>-15.24232028354113</v>
+        <v>-12.62107197436325</v>
       </c>
       <c r="F10">
-        <v>4.730311164824927</v>
+        <v>5.237562667304689</v>
       </c>
       <c r="G10">
-        <v>-10.24224308261294</v>
+        <v>-10.83147384096566</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-6.587379799959242</v>
       </c>
       <c r="E11">
-        <v>-16.05798449332871</v>
+        <v>-14.4632280298395</v>
       </c>
       <c r="F11">
-        <v>4.86546779506036</v>
+        <v>5.267092447803973</v>
       </c>
       <c r="G11">
-        <v>-8.437588566608808</v>
+        <v>-9.107732368486857</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-5.816130552870703</v>
       </c>
       <c r="E12">
-        <v>-16.99359892263146</v>
+        <v>-15.73625000050576</v>
       </c>
       <c r="F12">
-        <v>4.503388279025271</v>
+        <v>5.253640449758231</v>
       </c>
       <c r="G12">
-        <v>-7.715565205584841</v>
+        <v>-8.703859054877929</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-5.010904340497695</v>
       </c>
       <c r="E13">
-        <v>-16.57888580148302</v>
+        <v>-14.73452890763904</v>
       </c>
       <c r="F13">
-        <v>5.083838668916644</v>
+        <v>5.402009938446175</v>
       </c>
       <c r="G13">
-        <v>-7.31997156636963</v>
+        <v>-7.363832984219434</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-4.190526450012523</v>
       </c>
       <c r="E14">
-        <v>-17.9124987543719</v>
+        <v>-16.23001216393209</v>
       </c>
       <c r="F14">
-        <v>4.90289234954811</v>
+        <v>5.55131698103606</v>
       </c>
       <c r="G14">
-        <v>-7.287558014994627</v>
+        <v>-8.047897630090118</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-3.359438553634784</v>
       </c>
       <c r="E15">
-        <v>-18.8532213023553</v>
+        <v>-18.35332305664857</v>
       </c>
       <c r="F15">
-        <v>5.392216301065098</v>
+        <v>5.887799058359902</v>
       </c>
       <c r="G15">
-        <v>-6.416090007236879</v>
+        <v>-6.115247491901149</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-2.541801377995947</v>
       </c>
       <c r="E16">
-        <v>-19.83476351504384</v>
+        <v>-19.3607137989729</v>
       </c>
       <c r="F16">
-        <v>5.102839972490087</v>
+        <v>5.376791005448718</v>
       </c>
       <c r="G16">
-        <v>-5.665109304380906</v>
+        <v>-5.357248432501922</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-1.751092799540956</v>
       </c>
       <c r="E17">
-        <v>-20.34703355173953</v>
+        <v>-19.47689632811369</v>
       </c>
       <c r="F17">
-        <v>4.896521100650297</v>
+        <v>5.523204617331094</v>
       </c>
       <c r="G17">
-        <v>-5.471472185243395</v>
+        <v>-4.996349310538274</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-1.010726607043</v>
       </c>
       <c r="E18">
-        <v>-21.88549202636538</v>
+        <v>-20.06411260963632</v>
       </c>
       <c r="F18">
-        <v>5.551689151926189</v>
+        <v>5.705799574557601</v>
       </c>
       <c r="G18">
-        <v>-4.678159536576763</v>
+        <v>-4.880728507579227</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-0.3417725673802664</v>
       </c>
       <c r="E19">
-        <v>-22.71664361725919</v>
+        <v>-19.81386007902444</v>
       </c>
       <c r="F19">
-        <v>5.419414866456855</v>
+        <v>6.176648012865073</v>
       </c>
       <c r="G19">
-        <v>-4.208389814008642</v>
+        <v>-4.746730866331687</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>0.2350437819212442</v>
       </c>
       <c r="E20">
-        <v>-23.50124702382816</v>
+        <v>-21.99703286964831</v>
       </c>
       <c r="F20">
-        <v>5.392433268775513</v>
+        <v>6.312232243697674</v>
       </c>
       <c r="G20">
-        <v>-3.599166671144262</v>
+        <v>-4.585954222216982</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>0.6948500068669264</v>
       </c>
       <c r="E21">
-        <v>-23.01639236877491</v>
+        <v>-22.25513324571548</v>
       </c>
       <c r="F21">
-        <v>5.500459432973553</v>
+        <v>5.243834142729829</v>
       </c>
       <c r="G21">
-        <v>-3.799358670449529</v>
+        <v>-4.547684315783006</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>1.026444312522252</v>
       </c>
       <c r="E22">
-        <v>-24.29709010288416</v>
+        <v>-22.39465552989181</v>
       </c>
       <c r="F22">
-        <v>5.610444641388992</v>
+        <v>5.779522668627223</v>
       </c>
       <c r="G22">
-        <v>-3.365359392433234</v>
+        <v>-2.761489401705855</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>1.212619265009982</v>
       </c>
       <c r="E23">
-        <v>-24.33295561702491</v>
+        <v>-22.10199384019809</v>
       </c>
       <c r="F23">
-        <v>5.085537985363911</v>
+        <v>5.744042905003633</v>
       </c>
       <c r="G23">
-        <v>-2.681437100020739</v>
+        <v>-3.565627534285905</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>1.254510279613534</v>
       </c>
       <c r="E24">
-        <v>-24.22680818628512</v>
+        <v>-23.62221614999505</v>
       </c>
       <c r="F24">
-        <v>4.890355733521491</v>
+        <v>6.006584920547438</v>
       </c>
       <c r="G24">
-        <v>-3.136421926210474</v>
+        <v>-3.25799509004913</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>1.1550922764247</v>
       </c>
       <c r="E25">
-        <v>-25.59633193805482</v>
+        <v>-24.44964533525456</v>
       </c>
       <c r="F25">
-        <v>4.984507050194367</v>
+        <v>5.268842442840534</v>
       </c>
       <c r="G25">
-        <v>-2.447368288212109</v>
+        <v>-3.190327539226427</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>0.9295314333055616</v>
       </c>
       <c r="E26">
-        <v>-25.16405286623063</v>
+        <v>-25.31531748350884</v>
       </c>
       <c r="F26">
-        <v>4.446249753302131</v>
+        <v>5.01152982422951</v>
       </c>
       <c r="G26">
-        <v>-1.934230419079535</v>
+        <v>-2.098042833453752</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>0.5992460089003734</v>
       </c>
       <c r="E27">
-        <v>-24.58634638012411</v>
+        <v>-24.14034603205667</v>
       </c>
       <c r="F27">
-        <v>4.489012980430827</v>
+        <v>4.867745164166762</v>
       </c>
       <c r="G27">
-        <v>-2.062183004172367</v>
+        <v>-3.284118604899519</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>0.1834635081860087</v>
       </c>
       <c r="E28">
-        <v>-26.01291079049443</v>
+        <v>-23.50926242282173</v>
       </c>
       <c r="F28">
-        <v>4.682982113542019</v>
+        <v>5.354212110212297</v>
       </c>
       <c r="G28">
-        <v>-2.037009615891749</v>
+        <v>-1.808674668957136</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-0.2921715139380511</v>
       </c>
       <c r="E29">
-        <v>-24.82526866876879</v>
+        <v>-24.03137736201009</v>
       </c>
       <c r="F29">
-        <v>4.393029316013788</v>
+        <v>4.765097265257555</v>
       </c>
       <c r="G29">
-        <v>-1.863447644904378</v>
+        <v>-1.3238055481844</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-0.8158804706239944</v>
       </c>
       <c r="E30">
-        <v>-25.05279278833617</v>
+        <v>-24.49058726875791</v>
       </c>
       <c r="F30">
-        <v>4.592674451125916</v>
+        <v>5.169015124166724</v>
       </c>
       <c r="G30">
-        <v>-2.352445015964586</v>
+        <v>-2.669582036444609</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-1.371592789476327</v>
       </c>
       <c r="E31">
-        <v>-23.5774929406953</v>
+        <v>-24.66228436075873</v>
       </c>
       <c r="F31">
-        <v>4.659433990285351</v>
+        <v>5.141512487239202</v>
       </c>
       <c r="G31">
-        <v>-2.332979008193671</v>
+        <v>-2.096559709052159</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-1.955071062842435</v>
       </c>
       <c r="E32">
-        <v>-23.77877002491423</v>
+        <v>-24.54818040118746</v>
       </c>
       <c r="F32">
-        <v>4.630941537160679</v>
+        <v>4.981079910593356</v>
       </c>
       <c r="G32">
-        <v>-2.513701689182485</v>
+        <v>-2.389420499092706</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-2.561307581950582</v>
       </c>
       <c r="E33">
-        <v>-23.62728804088364</v>
+        <v>-23.74689862484824</v>
       </c>
       <c r="F33">
-        <v>4.538543382936195</v>
+        <v>5.022069387096759</v>
       </c>
       <c r="G33">
-        <v>-2.446742595105186</v>
+        <v>-3.615421449742083</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-3.185879195276603</v>
       </c>
       <c r="E34">
-        <v>-23.72370378098096</v>
+        <v>-22.19408941609208</v>
       </c>
       <c r="F34">
-        <v>4.568896690511508</v>
+        <v>5.193660755622792</v>
       </c>
       <c r="G34">
-        <v>-2.992337052704774</v>
+        <v>-2.328317760074377</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-3.828605454239881</v>
       </c>
       <c r="E35">
-        <v>-22.29343055039835</v>
+        <v>-21.94942502240567</v>
       </c>
       <c r="F35">
-        <v>5.12568176290847</v>
+        <v>5.266820050386518</v>
       </c>
       <c r="G35">
-        <v>-3.351769602994526</v>
+        <v>-3.27039639363924</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-4.479613263957864</v>
       </c>
       <c r="E36">
-        <v>-21.47889393063868</v>
+        <v>-22.53843910810935</v>
       </c>
       <c r="F36">
-        <v>5.172410589649426</v>
+        <v>5.563291381462698</v>
       </c>
       <c r="G36">
-        <v>-3.801682673418098</v>
+        <v>-2.865354457454949</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-5.139476078955253</v>
       </c>
       <c r="E37">
-        <v>-21.3495471275576</v>
+        <v>-22.04926428885278</v>
       </c>
       <c r="F37">
-        <v>5.124224753466265</v>
+        <v>5.244331426387277</v>
       </c>
       <c r="G37">
-        <v>-4.056564885032126</v>
+        <v>-4.981488271612485</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-5.792928510671353</v>
       </c>
       <c r="E38">
-        <v>-21.22944746840017</v>
+        <v>-19.76850741183762</v>
       </c>
       <c r="F38">
-        <v>5.510565060419973</v>
+        <v>5.977973689479109</v>
       </c>
       <c r="G38">
-        <v>-4.491219651065197</v>
+        <v>-3.738007640515756</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-6.442377353981157</v>
       </c>
       <c r="E39">
-        <v>-20.06539416778049</v>
+        <v>-19.79934631982985</v>
       </c>
       <c r="F39">
-        <v>5.731701084804613</v>
+        <v>6.16750527861524</v>
       </c>
       <c r="G39">
-        <v>-4.5418080974508</v>
+        <v>-4.999593645166759</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-7.074993512948711</v>
       </c>
       <c r="E40">
-        <v>-19.98783952192512</v>
+        <v>-19.47550608659333</v>
       </c>
       <c r="F40">
-        <v>5.76078901135349</v>
+        <v>6.068491984781966</v>
       </c>
       <c r="G40">
-        <v>-4.191433199756495</v>
+        <v>-4.024810132219437</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-7.694075248240199</v>
       </c>
       <c r="E41">
-        <v>-18.84540515621806</v>
+        <v>-18.71916035783223</v>
       </c>
       <c r="F41">
-        <v>5.629281239547229</v>
+        <v>6.356845239335604</v>
       </c>
       <c r="G41">
-        <v>-5.256220514279983</v>
+        <v>-5.764068131640801</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-8.294553696771528</v>
       </c>
       <c r="E42">
-        <v>-18.79354507188222</v>
+        <v>-17.59901514119092</v>
       </c>
       <c r="F42">
-        <v>5.804728931977357</v>
+        <v>6.459141555531584</v>
       </c>
       <c r="G42">
-        <v>-5.322040780691773</v>
+        <v>-5.052340567243967</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-8.87612299700201</v>
       </c>
       <c r="E43">
-        <v>-17.2066907955364</v>
+        <v>-17.82384029024973</v>
       </c>
       <c r="F43">
-        <v>5.73871690201001</v>
+        <v>6.699245625665443</v>
       </c>
       <c r="G43">
-        <v>-5.844269407875185</v>
+        <v>-4.779531751534786</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-9.439478045694852</v>
       </c>
       <c r="E44">
-        <v>-17.17206608327375</v>
+        <v>-17.14278044186615</v>
       </c>
       <c r="F44">
-        <v>5.851825178490695</v>
+        <v>6.648134684656466</v>
       </c>
       <c r="G44">
-        <v>-6.857855825088305</v>
+        <v>-5.617937340991832</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-9.977610663599057</v>
       </c>
       <c r="E45">
-        <v>-16.79349018470652</v>
+        <v>-18.12177312368837</v>
       </c>
       <c r="F45">
-        <v>6.105053419545801</v>
+        <v>6.415277652791658</v>
       </c>
       <c r="G45">
-        <v>-6.849043152862765</v>
+        <v>-4.824581655233188</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-10.49485711912399</v>
       </c>
       <c r="E46">
-        <v>-15.98829127835067</v>
+        <v>-15.43031535349556</v>
       </c>
       <c r="F46">
-        <v>5.879750664897639</v>
+        <v>6.032709733328527</v>
       </c>
       <c r="G46">
-        <v>-6.680423826365526</v>
+        <v>-6.033321421440805</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-10.97666993383491</v>
       </c>
       <c r="E47">
-        <v>-16.11459041842459</v>
+        <v>-16.83576348956812</v>
       </c>
       <c r="F47">
-        <v>6.238257340387498</v>
+        <v>6.492185579457228</v>
       </c>
       <c r="G47">
-        <v>-6.734673736117563</v>
+        <v>-7.482423346527207</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-11.43064577164864</v>
       </c>
       <c r="E48">
-        <v>-14.720336670099</v>
+        <v>-14.68122424009475</v>
       </c>
       <c r="F48">
-        <v>6.245938314077379</v>
+        <v>6.314123188560709</v>
       </c>
       <c r="G48">
-        <v>-7.635698294449924</v>
+        <v>-7.833933761341482</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-11.83943557347921</v>
       </c>
       <c r="E49">
-        <v>-14.26023012549767</v>
+        <v>-15.31469435513172</v>
       </c>
       <c r="F49">
-        <v>6.204918747161582</v>
+        <v>6.719965250157137</v>
       </c>
       <c r="G49">
-        <v>-6.973628913142157</v>
+        <v>-7.295500013743338</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-12.21071228802323</v>
       </c>
       <c r="E50">
-        <v>-14.59397413138896</v>
+        <v>-15.19291916059146</v>
       </c>
       <c r="F50">
-        <v>6.35666944797899</v>
+        <v>6.460215308142252</v>
       </c>
       <c r="G50">
-        <v>-8.39606108336419</v>
+        <v>-7.265112516238368</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-12.53267677523026</v>
       </c>
       <c r="E51">
-        <v>-12.42286519552152</v>
+        <v>-14.72026421451487</v>
       </c>
       <c r="F51">
-        <v>6.309106008220597</v>
+        <v>6.719205071317726</v>
       </c>
       <c r="G51">
-        <v>-8.277732254154021</v>
+        <v>-7.383709499637218</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-12.80887368855317</v>
       </c>
       <c r="E52">
-        <v>-12.65572385746994</v>
+        <v>-12.63697597507819</v>
       </c>
       <c r="F52">
-        <v>6.258300722453299</v>
+        <v>6.701231592883404</v>
       </c>
       <c r="G52">
-        <v>-8.144108704552417</v>
+        <v>-7.271266820395873</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-13.03600835768352</v>
       </c>
       <c r="E53">
-        <v>-13.80654495703921</v>
+        <v>-13.51010199154909</v>
       </c>
       <c r="F53">
-        <v>6.607024846503489</v>
+        <v>6.603413997016286</v>
       </c>
       <c r="G53">
-        <v>-8.001689035452971</v>
+        <v>-7.636026038458311</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-13.21154633337743</v>
       </c>
       <c r="E54">
-        <v>-11.07158666552872</v>
+        <v>-13.20513190950253</v>
       </c>
       <c r="F54">
-        <v>6.247230618104378</v>
+        <v>6.630862787942683</v>
       </c>
       <c r="G54">
-        <v>-9.523460745671915</v>
+        <v>-7.548624325676013</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-13.34132658937753</v>
       </c>
       <c r="E55">
-        <v>-11.70172835217006</v>
+        <v>-11.34329510598894</v>
       </c>
       <c r="F55">
-        <v>6.215775051211919</v>
+        <v>6.620693812259646</v>
       </c>
       <c r="G55">
-        <v>-9.139440773661997</v>
+        <v>-8.08809096348241</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-13.41720392033745</v>
       </c>
       <c r="E56">
-        <v>-10.63617841816522</v>
+        <v>-11.33207807587194</v>
       </c>
       <c r="F56">
-        <v>6.536972782745855</v>
+        <v>6.86418542934663</v>
       </c>
       <c r="G56">
-        <v>-9.532677304453246</v>
+        <v>-7.221320619844889</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-13.4542790364079</v>
       </c>
       <c r="E57">
-        <v>-10.35045887912527</v>
+        <v>-10.36213328511704</v>
       </c>
       <c r="F57">
-        <v>6.540118022693918</v>
+        <v>6.730800966030574</v>
       </c>
       <c r="G57">
-        <v>-9.113059036259544</v>
+        <v>-7.906193038827155</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-13.44145690511826</v>
       </c>
       <c r="E58">
-        <v>-10.1969164394212</v>
+        <v>-11.98631124423409</v>
       </c>
       <c r="F58">
-        <v>6.297137942617621</v>
+        <v>6.658642573405406</v>
       </c>
       <c r="G58">
-        <v>-9.259401701823027</v>
+        <v>-9.288339180381797</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-13.39855133392494</v>
       </c>
       <c r="E59">
-        <v>-9.193510754223624</v>
+        <v>-9.263951167412937</v>
       </c>
       <c r="F59">
-        <v>6.65206069162084</v>
+        <v>7.016235450582056</v>
       </c>
       <c r="G59">
-        <v>-8.698886615477944</v>
+        <v>-8.523106578979261</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-13.31743494771257</v>
       </c>
       <c r="E60">
-        <v>-9.632360641832951</v>
+        <v>-8.933445020437123</v>
       </c>
       <c r="F60">
-        <v>6.418628774508727</v>
+        <v>6.752542080837727</v>
       </c>
       <c r="G60">
-        <v>-9.715575013861361</v>
+        <v>-8.883631609296973</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-13.21205439822237</v>
       </c>
       <c r="E61">
-        <v>-10.26063206870912</v>
+        <v>-9.008862226560865</v>
       </c>
       <c r="F61">
-        <v>6.509729873588466</v>
+        <v>6.364435941788305</v>
       </c>
       <c r="G61">
-        <v>-9.214275655577222</v>
+        <v>-9.067886642376189</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-13.08036289653807</v>
       </c>
       <c r="E62">
-        <v>-10.16183435128378</v>
+        <v>-10.43669913812735</v>
       </c>
       <c r="F62">
-        <v>6.60848977447527</v>
+        <v>6.496342807485257</v>
       </c>
       <c r="G62">
-        <v>-9.420582232493523</v>
+        <v>-10.01878787980321</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-12.92716299641722</v>
       </c>
       <c r="E63">
-        <v>-9.947619416824939</v>
+        <v>-10.66585803681149</v>
       </c>
       <c r="F63">
-        <v>6.0776758953856</v>
+        <v>6.477694670330957</v>
       </c>
       <c r="G63">
-        <v>-9.289034394945043</v>
+        <v>-9.332184045503904</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-12.75861148125524</v>
       </c>
       <c r="E64">
-        <v>-8.837654209752872</v>
+        <v>-9.029022992843014</v>
       </c>
       <c r="F64">
-        <v>5.975146774420049</v>
+        <v>7.058249584812749</v>
       </c>
       <c r="G64">
-        <v>-9.731538464451727</v>
+        <v>-8.901872715218357</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-12.57050924296198</v>
       </c>
       <c r="E65">
-        <v>-7.937334706865905</v>
+        <v>-9.580980575741924</v>
       </c>
       <c r="F65">
-        <v>6.084804155710993</v>
+        <v>6.496189188011459</v>
       </c>
       <c r="G65">
-        <v>-10.27888420064159</v>
+        <v>-9.748630811070983</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-12.37762752969375</v>
       </c>
       <c r="E66">
-        <v>-9.10198123758059</v>
+        <v>-8.471721810615053</v>
       </c>
       <c r="F66">
-        <v>6.196330309982153</v>
+        <v>6.791225681528251</v>
       </c>
       <c r="G66">
-        <v>-9.544327114205942</v>
+        <v>-8.793349721895508</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-12.16882894487092</v>
       </c>
       <c r="E67">
-        <v>-9.216198409002052</v>
+        <v>-9.31952007196106</v>
       </c>
       <c r="F67">
-        <v>6.05675989136039</v>
+        <v>6.546524113121871</v>
       </c>
       <c r="G67">
-        <v>-10.40001044083244</v>
+        <v>-9.265642080164554</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-11.96385356776785</v>
       </c>
       <c r="E68">
-        <v>-8.689849346616519</v>
+        <v>-8.812263055991865</v>
       </c>
       <c r="F68">
-        <v>6.171505719757641</v>
+        <v>5.953819006856826</v>
       </c>
       <c r="G68">
-        <v>-9.620615325612906</v>
+        <v>-9.421346968513095</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-11.752654252218</v>
       </c>
       <c r="E69">
-        <v>-9.182551847125062</v>
+        <v>-9.236893535217106</v>
       </c>
       <c r="F69">
-        <v>5.892895423995786</v>
+        <v>6.424714956341761</v>
       </c>
       <c r="G69">
-        <v>-9.194859305989397</v>
+        <v>-8.729307218438306</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-11.55147971368226</v>
       </c>
       <c r="E70">
-        <v>-8.850542246778701</v>
+        <v>-7.971230334813318</v>
       </c>
       <c r="F70">
-        <v>5.454411599776236</v>
+        <v>5.994900338303326</v>
       </c>
       <c r="G70">
-        <v>-9.443232985073216</v>
+        <v>-8.945383215240998</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-11.35750349901565</v>
       </c>
       <c r="E71">
-        <v>-8.647068852666058</v>
+        <v>-8.803654426903282</v>
       </c>
       <c r="F71">
-        <v>5.723114231331101</v>
+        <v>6.344498668018837</v>
       </c>
       <c r="G71">
-        <v>-9.669962317421282</v>
+        <v>-9.586321384371596</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-11.17759330775015</v>
       </c>
       <c r="E72">
-        <v>-9.754185649587299</v>
+        <v>-9.559814488230071</v>
       </c>
       <c r="F72">
-        <v>5.395462898191749</v>
+        <v>6.267579655411859</v>
       </c>
       <c r="G72">
-        <v>-9.039488782740321</v>
+        <v>-9.265956581990784</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-11.01558555054709</v>
       </c>
       <c r="E73">
-        <v>-9.891072361891158</v>
+        <v>-9.222932249851459</v>
       </c>
       <c r="F73">
-        <v>5.320670802629206</v>
+        <v>5.655699037922674</v>
       </c>
       <c r="G73">
-        <v>-9.166924922729025</v>
+        <v>-8.430748979524674</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-10.86612354089791</v>
       </c>
       <c r="E74">
-        <v>-8.760552411298276</v>
+        <v>-8.242725936995178</v>
       </c>
       <c r="F74">
-        <v>5.485320788127868</v>
+        <v>5.960142744577176</v>
       </c>
       <c r="G74">
-        <v>-8.631970558492656</v>
+        <v>-8.161558590089916</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-10.73566879212962</v>
       </c>
       <c r="E75">
-        <v>-9.979386661988746</v>
+        <v>-9.839877963234445</v>
       </c>
       <c r="F75">
-        <v>5.543194153395771</v>
+        <v>5.798040941896456</v>
       </c>
       <c r="G75">
-        <v>-8.541986620189725</v>
+        <v>-8.595806159021658</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-10.60654536183478</v>
       </c>
       <c r="E76">
-        <v>-9.609596002996392</v>
+        <v>-10.08876742317002</v>
       </c>
       <c r="F76">
-        <v>5.00509839450691</v>
+        <v>5.801230525610151</v>
       </c>
       <c r="G76">
-        <v>-8.411064475748168</v>
+        <v>-8.888481558512005</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-10.48540466427449</v>
       </c>
       <c r="E77">
-        <v>-10.88981371886083</v>
+        <v>-8.910114322349605</v>
       </c>
       <c r="F77">
-        <v>5.219730138696842</v>
+        <v>5.494385920787843</v>
       </c>
       <c r="G77">
-        <v>-8.887309625391103</v>
+        <v>-8.064797965068097</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-10.35068482146952</v>
       </c>
       <c r="E78">
-        <v>-11.67814405953811</v>
+        <v>-10.74504746178363</v>
       </c>
       <c r="F78">
-        <v>5.370172698428096</v>
+        <v>5.581380470428847</v>
       </c>
       <c r="G78">
-        <v>-8.091606762845116</v>
+        <v>-8.069935931745047</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-10.20305326372791</v>
       </c>
       <c r="E79">
-        <v>-11.57494919385132</v>
+        <v>-12.93055241652145</v>
       </c>
       <c r="F79">
-        <v>5.243530071194066</v>
+        <v>5.497117813491976</v>
       </c>
       <c r="G79">
-        <v>-8.545413034822872</v>
+        <v>-6.948286687039037</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-10.02407347698326</v>
       </c>
       <c r="E80">
-        <v>-12.40095190979841</v>
+        <v>-12.65296148832526</v>
       </c>
       <c r="F80">
-        <v>5.102461466776297</v>
+        <v>5.262148117935972</v>
       </c>
       <c r="G80">
-        <v>-7.357427078600945</v>
+        <v>-7.337841891190616</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-9.807210760228937</v>
       </c>
       <c r="E81">
-        <v>-12.24930237222954</v>
+        <v>-12.60150896665011</v>
       </c>
       <c r="F81">
-        <v>5.296508201477346</v>
+        <v>5.401911748679418</v>
       </c>
       <c r="G81">
-        <v>-7.630696060140085</v>
+        <v>-7.110609355920581</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-9.543007247471254</v>
       </c>
       <c r="E82">
-        <v>-13.12004641137242</v>
+        <v>-14.39175965305045</v>
       </c>
       <c r="F82">
-        <v>4.997509275760124</v>
+        <v>5.539637149909694</v>
       </c>
       <c r="G82">
-        <v>-6.890319034646398</v>
+        <v>-6.997779342851141</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-9.224157514363069</v>
       </c>
       <c r="E83">
-        <v>-15.28236557919096</v>
+        <v>-12.87565825460047</v>
       </c>
       <c r="F83">
-        <v>4.805294888803239</v>
+        <v>5.354432245334544</v>
       </c>
       <c r="G83">
-        <v>-6.925821325009542</v>
+        <v>-6.505627021892008</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-8.854847232515636</v>
       </c>
       <c r="E84">
-        <v>-14.7853972561672</v>
+        <v>-16.11108085106865</v>
       </c>
       <c r="F84">
-        <v>5.158830311424532</v>
+        <v>5.125312759430172</v>
       </c>
       <c r="G84">
-        <v>-6.317571482533708</v>
+        <v>-7.079606096945307</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-8.430786320794558</v>
       </c>
       <c r="E85">
-        <v>-17.29677572897099</v>
+        <v>-16.77540798799389</v>
       </c>
       <c r="F85">
-        <v>4.848696349415857</v>
+        <v>5.05182247013012</v>
       </c>
       <c r="G85">
-        <v>-6.419367447320758</v>
+        <v>-5.655194220490789</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-7.969846431174886</v>
       </c>
       <c r="E86">
-        <v>-18.36740208233842</v>
+        <v>-18.84861131581549</v>
       </c>
       <c r="F86">
-        <v>4.841430306675821</v>
+        <v>5.017901073127323</v>
       </c>
       <c r="G86">
-        <v>-6.176131734913886</v>
+        <v>-5.90492853379125</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-7.473797606736531</v>
       </c>
       <c r="E87">
-        <v>-19.22205192485803</v>
+        <v>-19.00411458476488</v>
       </c>
       <c r="F87">
-        <v>4.867811679815211</v>
+        <v>5.245033008107818</v>
       </c>
       <c r="G87">
-        <v>-5.355652749551993</v>
+        <v>-5.629381896921092</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-6.966296677069376</v>
       </c>
       <c r="E88">
-        <v>-20.88646537553322</v>
+        <v>-19.78577901170287</v>
       </c>
       <c r="F88">
-        <v>4.520291172260756</v>
+        <v>4.933980496668187</v>
       </c>
       <c r="G88">
-        <v>-5.34826361190834</v>
+        <v>-5.002321534691118</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-6.454357413802124</v>
       </c>
       <c r="E89">
-        <v>-22.49704432720523</v>
+        <v>-22.77912297314302</v>
       </c>
       <c r="F89">
-        <v>4.515411774335287</v>
+        <v>5.212809343846371</v>
       </c>
       <c r="G89">
-        <v>-4.971447386991875</v>
+        <v>-4.962972390411341</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-5.955735865225378</v>
       </c>
       <c r="E90">
-        <v>-23.24602222875586</v>
+        <v>-23.70036855441943</v>
       </c>
       <c r="F90">
-        <v>4.392615968769858</v>
+        <v>4.861649480098236</v>
       </c>
       <c r="G90">
-        <v>-4.423184629687635</v>
+        <v>-4.228504688705254</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-5.478900496562058</v>
       </c>
       <c r="E91">
-        <v>-24.69567732809129</v>
+        <v>-26.15553507936601</v>
       </c>
       <c r="F91">
-        <v>4.376737733261662</v>
+        <v>4.820411361766109</v>
       </c>
       <c r="G91">
-        <v>-4.130621788745622</v>
+        <v>-3.518127826888442</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-5.032211972889998</v>
       </c>
       <c r="E92">
-        <v>-26.96799312955615</v>
+        <v>-27.47559883802394</v>
       </c>
       <c r="F92">
-        <v>4.120912214505235</v>
+        <v>4.261429689264432</v>
       </c>
       <c r="G92">
-        <v>-3.962816856451044</v>
+        <v>-2.951716658937917</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-4.62253070238929</v>
       </c>
       <c r="E93">
-        <v>-30.16735548750125</v>
+        <v>-30.27800422140467</v>
       </c>
       <c r="F93">
-        <v>4.060854918779941</v>
+        <v>4.557178850443171</v>
       </c>
       <c r="G93">
-        <v>-4.083525967903951</v>
+        <v>-3.236459991316171</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-4.246044276797698</v>
       </c>
       <c r="E94">
-        <v>-31.92325996279041</v>
+        <v>-32.53272463711273</v>
       </c>
       <c r="F94">
-        <v>3.60950190029153</v>
+        <v>4.404623627020721</v>
       </c>
       <c r="G94">
-        <v>-3.444332456272548</v>
+        <v>-3.008267397839747</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-3.907181460853721</v>
       </c>
       <c r="E95">
-        <v>-33.28378337246988</v>
+        <v>-33.18581663002494</v>
       </c>
       <c r="F95">
-        <v>3.160286884788961</v>
+        <v>3.981642700007406</v>
       </c>
       <c r="G95">
-        <v>-4.277557041960635</v>
+        <v>-2.889488334436237</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-3.589064681341078</v>
       </c>
       <c r="E96">
-        <v>-35.25954526083144</v>
+        <v>-36.95752602508848</v>
       </c>
       <c r="F96">
-        <v>2.907728551336086</v>
+        <v>3.577886379101612</v>
       </c>
       <c r="G96">
-        <v>-2.776264366447623</v>
+        <v>-2.051393936259882</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-3.293556698335705</v>
       </c>
       <c r="E97">
-        <v>-37.51202861037971</v>
+        <v>-39.23273552144425</v>
       </c>
       <c r="F97">
-        <v>3.117346282597736</v>
+        <v>3.341233204157495</v>
       </c>
       <c r="G97">
-        <v>-2.953368621162013</v>
+        <v>-2.816835102031391</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-2.994538317146993</v>
       </c>
       <c r="E98">
-        <v>-40.03934731169049</v>
+        <v>-41.21701999788824</v>
       </c>
       <c r="F98">
-        <v>2.283154530934654</v>
+        <v>3.345461698951719</v>
       </c>
       <c r="G98">
-        <v>-3.262229277793858</v>
+        <v>-2.58908612165723</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-2.694069797042749</v>
       </c>
       <c r="E99">
-        <v>-42.07407219586892</v>
+        <v>-43.74755165150747</v>
       </c>
       <c r="F99">
-        <v>2.142928458063899</v>
+        <v>2.647066394713907</v>
       </c>
       <c r="G99">
-        <v>-3.562598385117472</v>
+        <v>-2.162651440198169</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-2.355359698844394</v>
       </c>
       <c r="E100">
-        <v>-44.98048757025783</v>
+        <v>-46.08653564731326</v>
       </c>
       <c r="F100">
-        <v>1.737770557422941</v>
+        <v>2.285739138988651</v>
       </c>
       <c r="G100">
-        <v>-3.684807173699668</v>
+        <v>-4.231053808770493</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-1.99738238364704</v>
       </c>
       <c r="E101">
-        <v>-47.19145160586677</v>
+        <v>-46.67004537286061</v>
       </c>
       <c r="F101">
-        <v>1.713517685033901</v>
+        <v>2.376450646413192</v>
       </c>
       <c r="G101">
-        <v>-4.116614870568966</v>
+        <v>-2.82928606380459</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-1.558818374160337</v>
       </c>
       <c r="E102">
-        <v>-48.22467729240486</v>
+        <v>-50.62721389243429</v>
       </c>
       <c r="F102">
-        <v>1.617746237209531</v>
+        <v>1.505266691977275</v>
       </c>
       <c r="G102">
-        <v>-3.764786643382921</v>
+        <v>-2.740616412080751</v>
       </c>
     </row>
   </sheetData>
